--- a/outputs/daily/hr_rankings_2026-07-27_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-27_full.xlsx
@@ -55131,27 +55131,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>650968</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Yohel Pozo</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-07-28T01:40:00Z</t>
+          <t>2026-07-27T22:40:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -55166,12 +55166,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>678022</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -55180,7 +55180,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55198,13 +55198,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q200" t="n">
-        <v>38.5</v>
+        <v>37.9</v>
       </c>
       <c r="R200" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S200" t="n">
         <v>40.2</v>
@@ -55213,7 +55213,7 @@
         <v>50</v>
       </c>
       <c r="U200" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -55269,12 +55269,12 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
@@ -55284,119 +55284,119 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Contact streak: 5/11 over last 7 games</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>29.28</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>85.85</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>98.8106</t>
+          <t>97.2061</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.0894</t>
+          <t>0.0711</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.2884</t>
+          <t>0.2536</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.0746</t>
+          <t>0.0649</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>88.75</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.3832</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1517</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr"/>
       <c r="BH200" t="inlineStr"/>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -55407,27 +55407,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-07-27T22:40:00Z</t>
+          <t>2026-07-28T01:40:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -55442,12 +55442,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -55456,7 +55456,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -55470,26 +55470,26 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="Q201" t="n">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
       <c r="R201" t="n">
-        <v>21.5</v>
+        <v>30.9</v>
       </c>
       <c r="S201" t="n">
         <v>40.2</v>
       </c>
       <c r="T201" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U201" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -55550,7 +55550,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
@@ -55560,119 +55560,119 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 2/15, 0 HR</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 8.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.85</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>97.5316</t>
+          <t>98.8106</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.0894</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2884</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.0746</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.4001</t>
+          <t>0.3832</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1517</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr"/>
       <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -55683,22 +55683,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>644433</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chadwick Tromp</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -55718,12 +55718,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>672456</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -55732,7 +55732,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>26.8</v>
+        <v>28.2</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -55746,26 +55746,26 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P202" t="n">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q202" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="R202" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S202" t="n">
         <v>40.2</v>
       </c>
       <c r="T202" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U202" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr"/>
@@ -55821,12 +55821,12 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55836,12 +55836,12 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 11.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
@@ -55851,104 +55851,104 @@
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>86.77</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>96.7639</t>
+          <t>97.5316</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>0.2441</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>0.0663</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>0.0738</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>88.75</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4001</t>
         </is>
       </c>
       <c r="BE202" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
       <c r="BH202" t="inlineStr"/>
       <c r="BI202" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ202" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-07-27_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-27_full.xlsx
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -20235,52 +20235,52 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-27T18:35:00Z</t>
+          <t>2026-07-27T23:40:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Max Fried</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>608331</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -20298,26 +20298,26 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>40.1</v>
+        <v>53.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>47.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R72" t="n">
-        <v>42.1</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="S72" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T72" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -20369,27 +20369,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 11.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.3% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20399,112 +20399,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>101.0677</t>
+          <t>102.5657</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4226</t>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.2131</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3459</t>
+          <t>0.3407</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>73.97</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.2353</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>32.51</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.2891</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.0802</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20515,56 +20515,56 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-27T23:40:00Z</t>
+          <t>2026-07-27T18:35:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Max Fried</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>608331</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20578,26 +20578,26 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>53.2</v>
+        <v>40.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>9.300000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="R73" t="n">
-        <v>76.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="S73" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T73" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>19.5</v>
+        <v>68.7</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20649,27 +20649,27 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.3% barrel, 4.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20679,112 +20679,112 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>102.5657</t>
+          <t>101.0677</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t>0.4226</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.2131</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.3407</t>
+          <t>0.3459</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>33.63</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.2353</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.2891</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.0802</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -33799,32 +33799,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-27T18:35:00Z</t>
+          <t>2026-07-27T23:10:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>695505</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -33862,26 +33862,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>24.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q121" t="n">
-        <v>47.1</v>
+        <v>38.6</v>
       </c>
       <c r="R121" t="n">
-        <v>42.1</v>
+        <v>80.3</v>
       </c>
       <c r="S121" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="T121" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U121" t="n">
-        <v>28.2</v>
+        <v>34.2</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33933,27 +33933,27 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 11.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -33963,112 +33963,112 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>38.19</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>99.2123</t>
+          <t>97.4836</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.4073</t>
+          <t>0.3552</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3259</t>
+          <t>0.2971</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.1231</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>39.19</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.3525</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -34079,32 +34079,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-27T23:10:00Z</t>
+          <t>2026-07-27T18:35:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -34128,7 +34128,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -34142,26 +34142,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>13.7</v>
+        <v>24.4</v>
       </c>
       <c r="Q122" t="n">
-        <v>38.6</v>
+        <v>47.1</v>
       </c>
       <c r="R122" t="n">
-        <v>80.3</v>
+        <v>42.1</v>
       </c>
       <c r="S122" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="T122" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U122" t="n">
-        <v>34.2</v>
+        <v>26.4</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -34213,27 +34213,27 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -34243,112 +34243,112 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>38.19</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>97.4836</t>
+          <t>99.2123</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t>0.4073</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.3259</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.1231</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.3525</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr"/>
@@ -51863,32 +51863,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>669701</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-28T01:40:00Z</t>
+          <t>2026-07-27T18:35:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -51898,17 +51898,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -51926,65 +51926,61 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>32.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q186" t="n">
-        <v>29.8</v>
+        <v>39</v>
       </c>
       <c r="R186" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="S186" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T186" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U186" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -52001,12 +51997,12 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
@@ -52016,12 +52012,12 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
@@ -52031,104 +52027,112 @@
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>31.31</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>103.8198</t>
+          <t>97.5334</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2848</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>69.17</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.0779</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.3913</t>
         </is>
       </c>
       <c r="BE186" t="inlineStr">
         <is>
-          <t>0.1387</t>
+          <t>0.1374</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>28.51</t>
-        </is>
-      </c>
-      <c r="BG186" t="inlineStr"/>
-      <c r="BH186" t="inlineStr"/>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -52139,32 +52143,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>669701</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-27T18:35:00Z</t>
+          <t>2026-07-28T01:40:00Z</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -52174,21 +52178,21 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -52202,61 +52206,65 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>17.5</v>
+        <v>32.4</v>
       </c>
       <c r="Q187" t="n">
-        <v>39</v>
+        <v>29.8</v>
       </c>
       <c r="R187" t="n">
-        <v>42.1</v>
+        <v>30.9</v>
       </c>
       <c r="S187" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T187" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U187" t="n">
         <v>0</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr">
+      <c r="Z187" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -52273,12 +52281,12 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -52288,12 +52296,12 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -52303,112 +52311,104 @@
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>97.5334</t>
+          <t>103.8198</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.2848</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>69.17</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.0779</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>0.3913</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="BE187" t="inlineStr">
         <is>
-          <t>0.1374</t>
+          <t>0.1387</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="BG187" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH187" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>28.51</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -53053,7 +53053,7 @@
         <v>50</v>
       </c>
       <c r="U190" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
@@ -53120,7 +53120,7 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
@@ -53803,47 +53803,47 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>808982</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-07-27T18:35:00Z</t>
+          <t>2026-07-28T01:45:00Z</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Brandon Sproat</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>687075</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -53866,58 +53866,62 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P193" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="Q193" t="n">
-        <v>39</v>
+        <v>36.9</v>
       </c>
       <c r="R193" t="n">
-        <v>42.1</v>
+        <v>19.3</v>
       </c>
       <c r="S193" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="T193" t="n">
         <v>80</v>
       </c>
       <c r="U193" t="n">
-        <v>29.4</v>
+        <v>34.9</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W193" t="inlineStr">
+      <c r="Z193" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC193" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -53942,22 +53946,22 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -53967,112 +53971,104 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>87.03</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>95.6085</t>
+          <t>96.5974</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3829</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>0.0405</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>0.2582</t>
+          <t>0.3168</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>66.65</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>0.0287</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>0.3913</t>
+          <t>0.3948</t>
         </is>
       </c>
       <c r="BE193" t="inlineStr">
         <is>
-          <t>0.1374</t>
+          <t>0.1465</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="BG193" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH193" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>22.55</t>
+        </is>
+      </c>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
       <c r="BI193" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ193" t="inlineStr"/>
@@ -54083,47 +54079,47 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>808982</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-07-28T01:45:00Z</t>
+          <t>2026-07-27T18:35:00Z</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Brandon Sproat</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>687075</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -54132,7 +54128,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -54146,62 +54142,58 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>11</v>
+        <v>3.1</v>
       </c>
       <c r="Q194" t="n">
-        <v>36.9</v>
+        <v>39</v>
       </c>
       <c r="R194" t="n">
-        <v>19.3</v>
+        <v>42.1</v>
       </c>
       <c r="S194" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T194" t="n">
         <v>80</v>
       </c>
       <c r="U194" t="n">
-        <v>34.9</v>
+        <v>27</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54226,22 +54218,22 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -54251,104 +54243,112 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>87.03</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>96.5974</t>
+          <t>95.6085</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>0.3829</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.0405</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>0.3168</t>
+          <t>0.2582</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>66.65</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.0287</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>0.3948</t>
+          <t>0.3913</t>
         </is>
       </c>
       <c r="BE194" t="inlineStr">
         <is>
-          <t>0.1465</t>
+          <t>0.1374</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>22.55</t>
-        </is>
-      </c>
-      <c r="BG194" t="inlineStr"/>
-      <c r="BH194" t="inlineStr"/>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH194" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI194" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ194" t="inlineStr"/>
